--- a/product-definitions/spreadsheet/snr-winds.xlsx
+++ b/product-definitions/spreadsheet/snr-winds.xlsx
@@ -293,7 +293,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -328,11 +328,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -349,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -374,7 +369,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -383,7 +378,7 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -401,15 +396,11 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1885,7 +1876,7 @@
       </c>
       <c r="I20" s="6"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="10" t="s">
         <v>30</v>
@@ -1895,13 +1886,13 @@
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="I22" s="6"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="15" t="s">
         <v>32</v>
       </c>
@@ -1909,7 +1900,7 @@
       <c r="C23" s="4"/>
       <c r="I23" s="6"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="4"/>
       <c r="B24" s="9" t="s">
         <v>13</v>
@@ -1919,7 +1910,7 @@
       </c>
       <c r="I24" s="6"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="4"/>
       <c r="B25" s="9" t="s">
         <v>15</v>
@@ -1929,7 +1920,7 @@
       </c>
       <c r="I25" s="6"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="4"/>
       <c r="B26" s="9" t="s">
         <v>2</v>
@@ -1939,7 +1930,7 @@
       </c>
       <c r="I26" s="6"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="4"/>
       <c r="B27" s="9" t="s">
         <v>17</v>
@@ -1950,7 +1941,7 @@
       </c>
       <c r="I27" s="6"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="4"/>
       <c r="B28" s="9" t="s">
         <v>18</v>
@@ -1960,7 +1951,7 @@
       </c>
       <c r="I28" s="6"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="4"/>
       <c r="B29" s="9" t="s">
         <v>25</v>
@@ -1970,7 +1961,7 @@
       </c>
       <c r="I29" s="6"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="4"/>
       <c r="B30" s="10" t="s">
         <v>20</v>
@@ -1980,7 +1971,7 @@
       </c>
       <c r="I30" s="6"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="4"/>
       <c r="B31" s="10" t="s">
         <v>22</v>
@@ -1990,7 +1981,7 @@
       </c>
       <c r="I31" s="6"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="4"/>
       <c r="B32" s="10" t="s">
         <v>34</v>
@@ -2000,7 +1991,7 @@
       </c>
       <c r="I32" s="6"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="4"/>
       <c r="B33" s="10" t="s">
         <v>30</v>
@@ -2010,18 +2001,18 @@
       </c>
       <c r="I33" s="6"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="I34" s="6"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="B36" s="9" t="s">
         <v>13</v>
       </c>
@@ -2029,7 +2020,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="B37" s="9" t="s">
         <v>15</v>
       </c>
@@ -2037,7 +2028,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="B38" s="9" t="s">
         <v>2</v>
       </c>
@@ -2045,7 +2036,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="B39" s="9" t="s">
         <v>17</v>
       </c>
@@ -2053,7 +2044,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="B40" s="9" t="s">
         <v>18</v>
       </c>
@@ -2061,7 +2052,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="B41" s="9" t="s">
         <v>25</v>
       </c>
@@ -2069,7 +2060,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="B42" s="9" t="s">
         <v>20</v>
       </c>
@@ -2077,7 +2068,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="B43" s="9" t="s">
         <v>22</v>
       </c>
@@ -2085,7 +2076,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="B44" s="9" t="s">
         <v>34</v>
       </c>
@@ -2093,7 +2084,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="B45" s="9" t="s">
         <v>30</v>
       </c>
@@ -2101,12 +2092,13 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47">
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="B48" s="9" t="s">
         <v>13</v>
       </c>
@@ -2114,7 +2106,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="B49" s="9" t="s">
         <v>15</v>
       </c>
@@ -2122,7 +2114,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="B50" s="9" t="s">
         <v>2</v>
       </c>
@@ -2130,7 +2122,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="B51" s="9" t="s">
         <v>17</v>
       </c>
@@ -2138,7 +2130,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="B52" s="9" t="s">
         <v>18</v>
       </c>
@@ -2146,7 +2138,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="B53" s="9" t="s">
         <v>25</v>
       </c>
@@ -2154,7 +2146,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="B54" s="9" t="s">
         <v>20</v>
       </c>
@@ -2162,7 +2154,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="B55" s="9" t="s">
         <v>22</v>
       </c>
@@ -2170,7 +2162,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="B56" s="9" t="s">
         <v>34</v>
       </c>
@@ -2178,7 +2170,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="B57" s="9" t="s">
         <v>30</v>
       </c>
@@ -2186,12 +2178,13 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59">
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="B60" s="9" t="s">
         <v>13</v>
       </c>
@@ -2199,7 +2192,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="B61" s="9" t="s">
         <v>15</v>
       </c>
@@ -2207,7 +2200,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="B62" s="9" t="s">
         <v>2</v>
       </c>
@@ -2215,7 +2208,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="B63" s="9" t="s">
         <v>17</v>
       </c>
@@ -2223,7 +2216,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="B64" s="9" t="s">
         <v>18</v>
       </c>
@@ -2231,7 +2224,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="B65" s="9" t="s">
         <v>25</v>
       </c>
@@ -2239,7 +2232,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="B66" s="9" t="s">
         <v>20</v>
       </c>
@@ -2247,7 +2240,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="B67" s="9" t="s">
         <v>22</v>
       </c>
@@ -2255,7 +2248,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="B68" s="9" t="s">
         <v>34</v>
       </c>
@@ -2263,7 +2256,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="B69" s="9" t="s">
         <v>30</v>
       </c>
@@ -2271,12 +2264,13 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71">
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="B72" s="9" t="s">
         <v>13</v>
       </c>
@@ -2284,7 +2278,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="B73" s="9" t="s">
         <v>15</v>
       </c>
@@ -2292,7 +2286,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="B74" s="9" t="s">
         <v>2</v>
       </c>
@@ -2300,7 +2294,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="B75" s="9" t="s">
         <v>17</v>
       </c>
@@ -2308,7 +2302,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="B76" s="9" t="s">
         <v>18</v>
       </c>
@@ -2316,7 +2310,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="B77" s="9" t="s">
         <v>25</v>
       </c>
@@ -2324,7 +2318,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="B78" s="9" t="s">
         <v>20</v>
       </c>
@@ -2332,7 +2326,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="9" t="s">
         <v>22</v>
       </c>
@@ -2340,7 +2334,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="9" t="s">
         <v>34</v>
       </c>
@@ -2348,7 +2342,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="9" t="s">
         <v>30</v>
       </c>
@@ -2356,12 +2350,13 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83">
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="9" t="s">
         <v>13</v>
       </c>
@@ -2369,7 +2364,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="B85" s="9" t="s">
         <v>15</v>
       </c>
@@ -2377,7 +2372,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="B86" s="9" t="s">
         <v>2</v>
       </c>
@@ -2385,7 +2380,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="B87" s="9" t="s">
         <v>17</v>
       </c>
@@ -2393,7 +2388,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="B88" s="9" t="s">
         <v>18</v>
       </c>
@@ -2401,7 +2396,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="B89" s="9" t="s">
         <v>25</v>
       </c>
@@ -2409,7 +2404,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="B90" s="9" t="s">
         <v>20</v>
       </c>
@@ -2417,7 +2412,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="B91" s="9" t="s">
         <v>22</v>
       </c>
@@ -2425,7 +2420,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="B92" s="9" t="s">
         <v>34</v>
       </c>
@@ -2433,7 +2428,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="B93" s="9" t="s">
         <v>30</v>
       </c>
@@ -2441,12 +2436,13 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="19" t="s">
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="B96" s="9" t="s">
         <v>13</v>
       </c>
@@ -2454,7 +2450,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="B97" s="9" t="s">
         <v>15</v>
       </c>
@@ -2462,7 +2458,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="B98" s="9" t="s">
         <v>2</v>
       </c>
@@ -2470,16 +2466,16 @@
         <v>51</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="B99" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C99" s="6"/>
-      <c r="D99" s="19" t="s">
+      <c r="D99" s="9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="B100" s="9" t="s">
         <v>18</v>
       </c>
@@ -2487,7 +2483,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="B101" s="9" t="s">
         <v>25</v>
       </c>
@@ -2495,7 +2491,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="B102" s="9" t="s">
         <v>20</v>
       </c>
@@ -2503,7 +2499,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="B103" s="9" t="s">
         <v>22</v>
       </c>
@@ -2511,7 +2507,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="B104" s="9" t="s">
         <v>34</v>
       </c>
@@ -2519,7 +2515,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="B105" s="9" t="s">
         <v>30</v>
       </c>
@@ -2527,12 +2523,13 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="19" t="s">
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="B108" s="9" t="s">
         <v>13</v>
       </c>
@@ -2540,7 +2537,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="B109" s="9" t="s">
         <v>15</v>
       </c>
@@ -2548,7 +2545,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="B110" s="9" t="s">
         <v>2</v>
       </c>
@@ -2556,16 +2553,16 @@
         <v>51</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="B111" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C111" s="6"/>
-      <c r="D111" s="19" t="s">
+      <c r="D111" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="B112" s="9" t="s">
         <v>18</v>
       </c>
@@ -2573,7 +2570,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="B113" s="9" t="s">
         <v>25</v>
       </c>
@@ -2581,7 +2578,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="B114" s="9" t="s">
         <v>20</v>
       </c>
@@ -2589,7 +2586,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="B115" s="9" t="s">
         <v>22</v>
       </c>
@@ -2597,7 +2594,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="B116" s="9" t="s">
         <v>34</v>
       </c>
@@ -2605,7 +2602,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="B117" s="9" t="s">
         <v>30</v>
       </c>
@@ -2613,12 +2610,13 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="19" t="s">
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="B120" s="9" t="s">
         <v>13</v>
       </c>
@@ -2626,7 +2624,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="B121" s="9" t="s">
         <v>15</v>
       </c>
@@ -2634,7 +2632,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="B122" s="9" t="s">
         <v>2</v>
       </c>
@@ -2642,16 +2640,16 @@
         <v>51</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="B123" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C123" s="6"/>
-      <c r="D123" s="19" t="s">
+      <c r="D123" s="9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="B124" s="9" t="s">
         <v>18</v>
       </c>
@@ -2659,7 +2657,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="B125" s="9" t="s">
         <v>25</v>
       </c>
@@ -2667,7 +2665,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="B126" s="9" t="s">
         <v>20</v>
       </c>
@@ -2675,7 +2673,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="B127" s="9" t="s">
         <v>22</v>
       </c>
@@ -2683,7 +2681,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="B128" s="9" t="s">
         <v>34</v>
       </c>
@@ -2691,7 +2689,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="B129" s="9" t="s">
         <v>30</v>
       </c>
@@ -2699,12 +2697,13 @@
         <v>31</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="19" t="s">
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="B132" s="9" t="s">
         <v>13</v>
       </c>
@@ -2712,7 +2711,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="B133" s="9" t="s">
         <v>15</v>
       </c>
@@ -2720,7 +2719,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="B134" s="9" t="s">
         <v>2</v>
       </c>
@@ -2728,48 +2727,48 @@
         <v>51</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="B135" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C135" s="6"/>
-      <c r="D135" s="19" t="s">
+      <c r="D135" s="9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="20"/>
-      <c r="B136" s="20" t="s">
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="A136" s="19"/>
+      <c r="B136" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C136" s="20" t="s">
+      <c r="C136" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D136" s="20"/>
-      <c r="E136" s="20"/>
-      <c r="F136" s="20"/>
-      <c r="G136" s="20"/>
-      <c r="H136" s="20"/>
-      <c r="I136" s="20"/>
-      <c r="J136" s="20"/>
-      <c r="K136" s="20"/>
-      <c r="L136" s="20"/>
-      <c r="M136" s="20"/>
-      <c r="N136" s="20"/>
-      <c r="O136" s="20"/>
-      <c r="P136" s="20"/>
-      <c r="Q136" s="20"/>
-      <c r="R136" s="20"/>
-      <c r="S136" s="20"/>
-      <c r="T136" s="20"/>
-      <c r="U136" s="20"/>
-      <c r="V136" s="20"/>
-      <c r="W136" s="20"/>
-      <c r="X136" s="20"/>
-      <c r="Y136" s="20"/>
-      <c r="Z136" s="20"/>
-    </row>
-    <row r="137">
+      <c r="D136" s="19"/>
+      <c r="E136" s="19"/>
+      <c r="F136" s="19"/>
+      <c r="G136" s="19"/>
+      <c r="H136" s="19"/>
+      <c r="I136" s="19"/>
+      <c r="J136" s="19"/>
+      <c r="K136" s="19"/>
+      <c r="L136" s="19"/>
+      <c r="M136" s="19"/>
+      <c r="N136" s="19"/>
+      <c r="O136" s="19"/>
+      <c r="P136" s="19"/>
+      <c r="Q136" s="19"/>
+      <c r="R136" s="19"/>
+      <c r="S136" s="19"/>
+      <c r="T136" s="19"/>
+      <c r="U136" s="19"/>
+      <c r="V136" s="19"/>
+      <c r="W136" s="19"/>
+      <c r="X136" s="19"/>
+      <c r="Y136" s="19"/>
+      <c r="Z136" s="19"/>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
       <c r="B137" s="9" t="s">
         <v>25</v>
       </c>
@@ -2777,7 +2776,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="B138" s="9" t="s">
         <v>20</v>
       </c>
@@ -2785,7 +2784,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="B139" s="9" t="s">
         <v>22</v>
       </c>
@@ -2793,7 +2792,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="B140" s="9" t="s">
         <v>34</v>
       </c>
@@ -2801,7 +2800,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="B141" s="9" t="s">
         <v>30</v>
       </c>
@@ -2809,15 +2808,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="C142" s="6"/>
     </row>
-    <row r="143">
-      <c r="A143" s="19" t="s">
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="B144" s="9" t="s">
         <v>13</v>
       </c>
@@ -2825,7 +2824,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="B145" s="9" t="s">
         <v>15</v>
       </c>
@@ -2833,32 +2832,32 @@
         <v>37</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="B146" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C146" s="19" t="s">
+      <c r="C146" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="B147" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C147" s="6"/>
-      <c r="D147" s="19" t="s">
+      <c r="D147" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="B148" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C148" s="19" t="s">
+      <c r="C148" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="B149" s="9" t="s">
         <v>25</v>
       </c>
@@ -2866,7 +2865,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="B150" s="9" t="s">
         <v>20</v>
       </c>
@@ -2874,7 +2873,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="B151" s="9" t="s">
         <v>22</v>
       </c>
@@ -2882,7 +2881,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="B152" s="9" t="s">
         <v>34</v>
       </c>
@@ -2890,7 +2889,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="B153" s="9" t="s">
         <v>30</v>
       </c>
@@ -2898,15 +2897,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="C154" s="15"/>
     </row>
-    <row r="155">
-      <c r="A155" s="19" t="s">
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="A155" s="9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="B156" s="9" t="s">
         <v>13</v>
       </c>
@@ -2914,7 +2913,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="B157" s="9" t="s">
         <v>15</v>
       </c>
@@ -2922,32 +2921,32 @@
         <v>37</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="B158" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C158" s="19" t="s">
+      <c r="C158" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="B159" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C159" s="6"/>
-      <c r="D159" s="19" t="s">
+      <c r="D159" s="9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="B160" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C160" s="19" t="s">
+      <c r="C160" s="9" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="B161" s="9" t="s">
         <v>25</v>
       </c>
@@ -2955,7 +2954,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="B162" s="9" t="s">
         <v>20</v>
       </c>
@@ -2963,7 +2962,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="B163" s="9" t="s">
         <v>22</v>
       </c>
@@ -2971,7 +2970,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="B164" s="9" t="s">
         <v>34</v>
       </c>
@@ -2979,7 +2978,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="B165" s="9" t="s">
         <v>30</v>
       </c>
@@ -2987,15 +2986,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="C166" s="15"/>
     </row>
-    <row r="167">
-      <c r="A167" s="19" t="s">
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="A167" s="9" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="B168" s="9" t="s">
         <v>13</v>
       </c>
@@ -3003,7 +3002,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="B169" s="9" t="s">
         <v>15</v>
       </c>
@@ -3011,32 +3010,32 @@
         <v>37</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="B170" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C170" s="19" t="s">
+      <c r="C170" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="B171" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C171" s="6"/>
-      <c r="D171" s="19" t="s">
+      <c r="D171" s="9" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="B172" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C172" s="19" t="s">
+      <c r="C172" s="9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="B173" s="9" t="s">
         <v>25</v>
       </c>
@@ -3044,7 +3043,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="B174" s="9" t="s">
         <v>20</v>
       </c>
@@ -3052,7 +3051,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="B175" s="9" t="s">
         <v>22</v>
       </c>
@@ -3060,7 +3059,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="B176" s="9" t="s">
         <v>34</v>
       </c>
@@ -3068,7 +3067,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="B177" s="9" t="s">
         <v>30</v>
       </c>
@@ -3076,13 +3075,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="19" t="s">
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1">
+      <c r="A179" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C179" s="6"/>
     </row>
-    <row r="180">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="B180" s="9" t="s">
         <v>13</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="B181" s="9" t="s">
         <v>15</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="B182" s="9" t="s">
         <v>2</v>
       </c>
@@ -3106,24 +3106,24 @@
         <v>38</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="B183" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C183" s="6"/>
-      <c r="D183" s="19" t="s">
+      <c r="D183" s="9" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="B184" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C184" s="19" t="s">
+      <c r="C184" s="9" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="B185" s="9" t="s">
         <v>25</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="B186" s="9" t="s">
         <v>20</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="B187" s="9" t="s">
         <v>22</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="B188" s="9" t="s">
         <v>34</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="B189" s="9" t="s">
         <v>30</v>
       </c>
@@ -3163,13 +3163,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="19" t="s">
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1">
+      <c r="A191" s="9" t="s">
         <v>69</v>
       </c>
       <c r="C191" s="6"/>
     </row>
-    <row r="192">
+    <row r="192" ht="15.75" customHeight="1">
       <c r="B192" s="9" t="s">
         <v>13</v>
       </c>
@@ -3177,7 +3178,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" ht="15.75" customHeight="1">
       <c r="B193" s="9" t="s">
         <v>15</v>
       </c>
@@ -3185,7 +3186,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" ht="15.75" customHeight="1">
       <c r="B194" s="9" t="s">
         <v>2</v>
       </c>
@@ -3193,24 +3194,24 @@
         <v>38</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" ht="15.75" customHeight="1">
       <c r="B195" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C195" s="6"/>
-      <c r="D195" s="19" t="s">
+      <c r="D195" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" ht="15.75" customHeight="1">
       <c r="B196" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C196" s="19" t="s">
+      <c r="C196" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" ht="15.75" customHeight="1">
       <c r="B197" s="9" t="s">
         <v>25</v>
       </c>
@@ -3218,7 +3219,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" ht="15.75" customHeight="1">
       <c r="B198" s="9" t="s">
         <v>20</v>
       </c>
@@ -3226,7 +3227,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" ht="15.75" customHeight="1">
       <c r="B199" s="9" t="s">
         <v>22</v>
       </c>
@@ -3234,7 +3235,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" ht="15.75" customHeight="1">
       <c r="B200" s="9" t="s">
         <v>34</v>
       </c>
@@ -3242,7 +3243,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" ht="15.75" customHeight="1">
       <c r="B201" s="9" t="s">
         <v>30</v>
       </c>
@@ -3250,13 +3251,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="19" t="s">
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1">
+      <c r="A203" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C203" s="6"/>
     </row>
-    <row r="204">
+    <row r="204" ht="15.75" customHeight="1">
       <c r="B204" s="9" t="s">
         <v>13</v>
       </c>
@@ -3264,7 +3266,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" ht="15.75" customHeight="1">
       <c r="B205" s="9" t="s">
         <v>15</v>
       </c>
@@ -3272,7 +3274,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" ht="15.75" customHeight="1">
       <c r="B206" s="9" t="s">
         <v>2</v>
       </c>
@@ -3280,24 +3282,24 @@
         <v>38</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" ht="15.75" customHeight="1">
       <c r="B207" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C207" s="6"/>
-      <c r="D207" s="19" t="s">
+      <c r="D207" s="9" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" ht="15.75" customHeight="1">
       <c r="B208" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C208" s="19" t="s">
+      <c r="C208" s="9" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" ht="15.75" customHeight="1">
       <c r="B209" s="9" t="s">
         <v>25</v>
       </c>
@@ -3305,7 +3307,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" ht="15.75" customHeight="1">
       <c r="B210" s="9" t="s">
         <v>20</v>
       </c>
@@ -3313,7 +3315,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" ht="15.75" customHeight="1">
       <c r="B211" s="9" t="s">
         <v>22</v>
       </c>
@@ -3321,7 +3323,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" ht="15.75" customHeight="1">
       <c r="B212" s="9" t="s">
         <v>34</v>
       </c>
@@ -3329,7 +3331,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" ht="15.75" customHeight="1">
       <c r="B213" s="9" t="s">
         <v>30</v>
       </c>
@@ -3337,13 +3339,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="19" t="s">
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1">
+      <c r="A215" s="9" t="s">
         <v>73</v>
       </c>
       <c r="C215" s="6"/>
     </row>
-    <row r="216">
+    <row r="216" ht="15.75" customHeight="1">
       <c r="B216" s="9" t="s">
         <v>13</v>
       </c>
@@ -3351,7 +3354,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" ht="15.75" customHeight="1">
       <c r="B217" s="9" t="s">
         <v>15</v>
       </c>
@@ -3359,7 +3362,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" ht="15.75" customHeight="1">
       <c r="B218" s="9" t="s">
         <v>2</v>
       </c>
@@ -3367,13 +3370,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" ht="15.75" customHeight="1">
       <c r="B219" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C219" s="15"/>
     </row>
-    <row r="220">
+    <row r="220" ht="15.75" customHeight="1">
       <c r="B220" s="9" t="s">
         <v>18</v>
       </c>
@@ -3381,7 +3384,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" ht="15.75" customHeight="1">
       <c r="B221" s="10" t="s">
         <v>76</v>
       </c>
@@ -3389,21 +3392,22 @@
         <v>77</v>
       </c>
     </row>
-    <row r="222">
-      <c r="B222" s="21" t="s">
+    <row r="222" ht="15.75" customHeight="1">
+      <c r="B222" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C222" s="22" t="s">
+      <c r="C222" s="19" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="19" t="s">
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1">
+      <c r="A224" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C224" s="6"/>
     </row>
-    <row r="225">
+    <row r="225" ht="15.75" customHeight="1">
       <c r="B225" s="9" t="s">
         <v>13</v>
       </c>
@@ -3411,7 +3415,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" ht="15.75" customHeight="1">
       <c r="B226" s="9" t="s">
         <v>15</v>
       </c>
@@ -3419,7 +3423,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" ht="15.75" customHeight="1">
       <c r="B227" s="9" t="s">
         <v>2</v>
       </c>
@@ -3427,13 +3431,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" ht="15.75" customHeight="1">
       <c r="B228" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C228" s="15"/>
     </row>
-    <row r="229">
+    <row r="229" ht="15.75" customHeight="1">
       <c r="B229" s="9" t="s">
         <v>18</v>
       </c>
@@ -3441,7 +3445,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" ht="15.75" customHeight="1">
       <c r="B230" s="10" t="s">
         <v>76</v>
       </c>
@@ -3449,21 +3453,22 @@
         <v>77</v>
       </c>
     </row>
-    <row r="231">
-      <c r="B231" s="21" t="s">
+    <row r="231" ht="15.75" customHeight="1">
+      <c r="B231" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C231" s="22" t="s">
+      <c r="C231" s="19" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="19" t="s">
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1">
+      <c r="A233" s="9" t="s">
         <v>82</v>
       </c>
       <c r="C233" s="6"/>
     </row>
-    <row r="234">
+    <row r="234" ht="15.75" customHeight="1">
       <c r="B234" s="9" t="s">
         <v>13</v>
       </c>
@@ -3471,7 +3476,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" ht="15.75" customHeight="1">
       <c r="B235" s="9" t="s">
         <v>15</v>
       </c>
@@ -3479,7 +3484,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" ht="15.75" customHeight="1">
       <c r="B236" s="9" t="s">
         <v>2</v>
       </c>
@@ -3487,13 +3492,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" ht="15.75" customHeight="1">
       <c r="B237" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C237" s="15"/>
     </row>
-    <row r="238">
+    <row r="238" ht="15.75" customHeight="1">
       <c r="B238" s="9" t="s">
         <v>18</v>
       </c>
@@ -3501,7 +3506,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" ht="15.75" customHeight="1">
       <c r="B239" s="10" t="s">
         <v>76</v>
       </c>
@@ -3509,21 +3514,22 @@
         <v>77</v>
       </c>
     </row>
-    <row r="240">
-      <c r="B240" s="21" t="s">
+    <row r="240" ht="15.75" customHeight="1">
+      <c r="B240" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C240" s="22" t="s">
+      <c r="C240" s="19" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="19" t="s">
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1">
+      <c r="A242" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C242" s="6"/>
     </row>
-    <row r="243">
+    <row r="243" ht="15.75" customHeight="1">
       <c r="B243" s="9" t="s">
         <v>13</v>
       </c>
@@ -3531,7 +3537,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" ht="15.75" customHeight="1">
       <c r="B244" s="9" t="s">
         <v>15</v>
       </c>
@@ -3539,7 +3545,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" ht="15.75" customHeight="1">
       <c r="B245" s="9" t="s">
         <v>2</v>
       </c>
@@ -3547,13 +3553,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" ht="15.75" customHeight="1">
       <c r="B246" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C246" s="15"/>
     </row>
-    <row r="247">
+    <row r="247" ht="15.75" customHeight="1">
       <c r="B247" s="9" t="s">
         <v>18</v>
       </c>
@@ -3561,7 +3567,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" ht="15.75" customHeight="1">
       <c r="B248" s="10" t="s">
         <v>76</v>
       </c>
@@ -3569,20 +3575,21 @@
         <v>77</v>
       </c>
     </row>
-    <row r="249">
-      <c r="B249" s="21" t="s">
+    <row r="249" ht="15.75" customHeight="1">
+      <c r="B249" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C249" s="22" t="s">
+      <c r="C249" s="19" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="19" t="s">
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1">
+      <c r="A251" s="9" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" ht="15.75" customHeight="1">
       <c r="B252" s="9" t="s">
         <v>13</v>
       </c>
@@ -3590,7 +3597,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" ht="15.75" customHeight="1">
       <c r="B253" s="9" t="s">
         <v>15</v>
       </c>
@@ -3598,7 +3605,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" ht="15.75" customHeight="1">
       <c r="B254" s="9" t="s">
         <v>2</v>
       </c>
@@ -3606,13 +3613,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" ht="15.75" customHeight="1">
       <c r="B255" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C255" s="15"/>
     </row>
-    <row r="256">
+    <row r="256" ht="15.75" customHeight="1">
       <c r="B256" s="9" t="s">
         <v>18</v>
       </c>
@@ -3620,7 +3627,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" ht="15.75" customHeight="1">
       <c r="B257" s="10" t="s">
         <v>76</v>
       </c>
@@ -3628,11 +3635,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="258">
-      <c r="B258" s="21" t="s">
+    <row r="258" ht="15.75" customHeight="1">
+      <c r="B258" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C258" s="22" t="s">
+      <c r="C258" s="19" t="s">
         <v>88</v>
       </c>
     </row>
